--- a/DQOPS_Package_20260212/DQOps_290_Menu_Links.xlsx
+++ b/DQOPS_Package_20260212/DQOps_290_Menu_Links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GauravKalwani\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GKALWANI\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA14E85-2F9E-4C4E-9721-B01340EE4E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24958CA5-69B9-4958-8561-7663F635BB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="12780" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu_Links" sheetId="2" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="161">
   <si>
     <t>MenuLinkID</t>
   </si>
@@ -537,6 +537,15 @@
   </si>
   <si>
     <t>9000</t>
+  </si>
+  <si>
+    <t>5cf0277f-28fb-4bfa-ba89-7f8289dd1ac4</t>
+  </si>
+  <si>
+    <t>Users</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
 </sst>
 </file>
@@ -629,7 +638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -643,14 +652,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -965,7 +966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A778C87-EA36-46E5-96CB-48B43D1541A8}">
-  <dimension ref="A1:IV31"/>
+  <dimension ref="A1:IV32"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.1796875" style="2"/>
@@ -1412,279 +1413,290 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="G20" s="8" t="s">
+      <c r="E20" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="G21" s="8" t="s">
+      <c r="E21" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="G22" s="8" t="s">
+      <c r="E22" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E23" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="G23" s="8" t="s">
+      <c r="E23" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="G24" s="10" t="s">
+      <c r="E24" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F25" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="G25" s="10" t="s">
+      <c r="F25" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F26" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="G26" s="10" t="s">
+      <c r="F26" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="G27" s="10" t="s">
+      <c r="F27" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="G28" s="10" t="s">
+      <c r="F28" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D29" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F29" s="10" t="s">
+      <c r="D29" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G29" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D30" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F30" s="10" t="s">
+      <c r="D30" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>103</v>
+      <c r="E31" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2139,4 +2151,10 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{e760c494-6550-44b4-8258-77c175d778b7}" enabled="1" method="Privileged" siteId="{76a2ae5a-9f00-4f6b-95ed-5d33d77c4d61}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>